--- a/tabelas/back_scratch.xlsx
+++ b/tabelas/back_scratch.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Weigth</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -457,11 +457,6 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Calculated distance</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Weight</t>
         </is>
       </c>
     </row>
@@ -472,7 +467,9 @@
       <c r="B2" t="n">
         <v>1.74</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>82</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Male</t>
@@ -483,9 +480,6 @@
       </c>
       <c r="F2" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>82</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +489,9 @@
       <c r="B3" t="n">
         <v>1.74</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>82</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -506,9 +502,6 @@
       </c>
       <c r="F3" t="n">
         <v>-2.15</v>
-      </c>
-      <c r="G3" t="n">
-        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +511,9 @@
       <c r="B4" t="n">
         <v>1.74</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>82</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Male</t>
@@ -530,22 +525,17 @@
       <c r="F4" t="n">
         <v>-14.32</v>
       </c>
-      <c r="G4" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C5" t="n">
         <v>82</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Male</t>
@@ -554,14 +544,301 @@
       <c r="E5" t="n">
         <v>-10</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-9.85</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>82</t>
+      <c r="F5" t="n">
+        <v>-9.85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-9.58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C7" t="n">
+        <v>82</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-5.78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C8" t="n">
+        <v>82</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-4.84</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C9" t="n">
+        <v>82</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C10" t="n">
+        <v>82</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-9.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-6.87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-18.48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-13.63</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-4.54</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-16.61</t>
         </is>
       </c>
     </row>
